--- a/App_Data/templates/sample_inspection.xlsx
+++ b/App_Data/templates/sample_inspection.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部檢驗紀錄表" sheetId="1" r:id="R65e2e90dadba4277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部檢驗紀錄表" sheetId="1" r:id="Rbb95715b067f451b"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm.Print_Titles">'外部檢驗紀錄表'!$1:$9</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles">'外部檢驗紀錄表'!$1:$10</x:definedName>
   </x:definedNames>
 </x:workbook>
 </file>
@@ -32,7 +32,7 @@
       <x:name val="微軟正黑體"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -42,6 +42,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9D9D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -69,7 +74,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellXfs count="6">
+  <x:cellXfs count="8">
     <x:xf fontId="0" fillId="0" borderId="0"/>
     <x:xf fontId="1" fillId="0" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,6 +91,12 @@
     <x:xf fontId="3" fillId="0" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf fontId="0" fillId="0" borderId="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
 </x:styleSheet>
 </file>
@@ -95,7 +106,7 @@
   <x:sheetPr>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:U10"/>
+  <x:dimension ref="A1:U11"/>
   <x:sheetFormatPr defaultColWidth="10" defaultRowHeight="18"/>
   <x:cols>
     <x:col min="1" max="1" width="6" customWidth="1"/>
@@ -163,16 +174,16 @@
       <x:c r="Q1" s="1" t="str">
         <x:v/>
       </x:c>
-      <x:c r="R1" s="1" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="S1" s="1" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="T1" s="1" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U1" s="1" t="str">
+      <x:c r="R1" s="7" t="str">
+        <x:v>[[photo]]</x:v>
+      </x:c>
+      <x:c r="S1" s="7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="T1" s="7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U1" s="7" t="str">
         <x:v/>
       </x:c>
     </x:row>
@@ -184,7 +195,7 @@
         <x:v/>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>{{docNo}}{{_str}}</x:v>
+        <x:v>{{docNo}}</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v/>
@@ -205,7 +216,7 @@
         <x:v/>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>{{seqNo}}{{_str}}</x:v>
+        <x:v>{{seqNo}}</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
         <x:v/>
@@ -226,7 +237,7 @@
         <x:v/>
       </x:c>
       <x:c r="Q2" s="3" t="str">
-        <x:v>{{sourceDoc}}{{_str}}</x:v>
+        <x:v>{{sourceDoc}}</x:v>
       </x:c>
       <x:c r="R2" s="3" t="str">
         <x:v/>
@@ -245,11 +256,11 @@
       <x:c r="A3" s="2" t="str">
         <x:v>品號</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v/>
+      <x:c r="B3" s="3" t="str">
+        <x:v>{{partNo}}</x:v>
       </x:c>
       <x:c r="C3" s="3" t="str">
-        <x:v>{{partNo}}{{_str}}</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v/>
@@ -257,26 +268,26 @@
       <x:c r="E3" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="F3" s="3" t="str">
-        <x:v/>
+      <x:c r="F3" s="2" t="str">
+        <x:v>QC模組</x:v>
       </x:c>
       <x:c r="G3" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H3" s="2" t="str">
-        <x:v>QC模組</x:v>
-      </x:c>
-      <x:c r="I3" s="2" t="str">
+        <x:v>{{qcModule}}</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
         <x:v/>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>{{qcModule}}{{_str}}</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="str">
-        <x:v/>
+        <x:v/>
+      </x:c>
+      <x:c r="K3" s="2" t="str">
+        <x:v>製程代碼</x:v>
       </x:c>
       <x:c r="L3" s="3" t="str">
-        <x:v/>
+        <x:v>{{processCode}}</x:v>
       </x:c>
       <x:c r="M3" s="3" t="str">
         <x:v/>
@@ -284,14 +295,14 @@
       <x:c r="N3" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="O3" s="2" t="str">
-        <x:v>製程代碼</x:v>
+      <x:c r="O3" s="3" t="str">
+        <x:v/>
       </x:c>
       <x:c r="P3" s="2" t="str">
-        <x:v/>
+        <x:v>數量</x:v>
       </x:c>
       <x:c r="Q3" s="3" t="str">
-        <x:v>{{processCode}}{{_str}}</x:v>
+        <x:v>{{qty}}</x:v>
       </x:c>
       <x:c r="R3" s="3" t="str">
         <x:v/>
@@ -308,13 +319,13 @@
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="2" t="str">
-        <x:v>數量</x:v>
+        <x:v>品名</x:v>
       </x:c>
       <x:c r="B4" s="2" t="str">
         <x:v/>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>{{qty}}{{_str}}</x:v>
+        <x:v>{{partName}}</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
         <x:v/>
@@ -328,35 +339,35 @@
       <x:c r="G4" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="H4" s="2" t="str">
-        <x:v>品名</x:v>
-      </x:c>
-      <x:c r="I4" s="2" t="str">
+      <x:c r="H4" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="I4" s="3" t="str">
         <x:v/>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>{{partName}}{{_str}}</x:v>
-      </x:c>
-      <x:c r="K4" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="L4" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="K4" s="2" t="str">
+        <x:v>製程名稱</x:v>
+      </x:c>
+      <x:c r="L4" s="2" t="str">
         <x:v/>
       </x:c>
       <x:c r="M4" s="3" t="str">
-        <x:v/>
+        <x:v>{{processName}}</x:v>
       </x:c>
       <x:c r="N4" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="O4" s="2" t="str">
-        <x:v>製程名稱</x:v>
-      </x:c>
-      <x:c r="P4" s="2" t="str">
+      <x:c r="O4" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="P4" s="3" t="str">
         <x:v/>
       </x:c>
       <x:c r="Q4" s="3" t="str">
-        <x:v>{{processName}}{{_str}}</x:v>
+        <x:v/>
       </x:c>
       <x:c r="R4" s="3" t="str">
         <x:v/>
@@ -379,7 +390,7 @@
         <x:v/>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>{{spec}}{{_str}}</x:v>
+        <x:v>{{spec}}</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
         <x:v/>
@@ -440,11 +451,11 @@
       <x:c r="A6" s="2" t="str">
         <x:v>檢驗點</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v/>
+      <x:c r="B6" s="3" t="str">
+        <x:v>{{inspectPoint}}</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>{{inspectPoint}}{{_str}}</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D6" s="3" t="str">
         <x:v/>
@@ -452,26 +463,26 @@
       <x:c r="E6" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="F6" s="3" t="str">
-        <x:v/>
+      <x:c r="F6" s="2" t="str">
+        <x:v>廠商</x:v>
       </x:c>
       <x:c r="G6" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H6" s="2" t="str">
-        <x:v>廠商</x:v>
-      </x:c>
-      <x:c r="I6" s="2" t="str">
+        <x:v>{{vendor}}</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="I6" s="3" t="str">
         <x:v/>
       </x:c>
       <x:c r="J6" s="3" t="str">
-        <x:v>{{vendor}}{{_str}}</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="str">
-        <x:v/>
+        <x:v/>
+      </x:c>
+      <x:c r="K6" s="2" t="str">
+        <x:v>備註</x:v>
       </x:c>
       <x:c r="L6" s="3" t="str">
-        <x:v/>
+        <x:v>{{remark}}</x:v>
       </x:c>
       <x:c r="M6" s="3" t="str">
         <x:v/>
@@ -479,14 +490,14 @@
       <x:c r="N6" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="O6" s="2" t="str">
-        <x:v>備註</x:v>
+      <x:c r="O6" s="3" t="str">
+        <x:v/>
       </x:c>
       <x:c r="P6" s="2" t="str">
-        <x:v/>
+        <x:v>日期</x:v>
       </x:c>
       <x:c r="Q6" s="3" t="str">
-        <x:v>{{remark}}{{_str}}</x:v>
+        <x:v>{{date}}</x:v>
       </x:c>
       <x:c r="R6" s="3" t="str">
         <x:v/>
@@ -503,13 +514,13 @@
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="2" t="str">
-        <x:v>日期</x:v>
+        <x:v>檢驗備註</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
         <x:v/>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>{{date}}{{_str}}</x:v>
+        <x:v>{{inspectRemark}}</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
         <x:v/>
@@ -523,14 +534,14 @@
       <x:c r="G7" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="H7" s="2" t="str">
-        <x:v>檢驗備註</x:v>
-      </x:c>
-      <x:c r="I7" s="2" t="str">
+      <x:c r="H7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="I7" s="3" t="str">
         <x:v/>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>{{inspectRemark}}{{_str}}</x:v>
+        <x:v/>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v/>
@@ -544,37 +555,37 @@
       <x:c r="N7" s="3" t="str">
         <x:v/>
       </x:c>
-      <x:c r="O7" s="2" t="str">
+      <x:c r="O7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="P7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="Q7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="R7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="T7" s="3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U7" s="3" t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
+      <x:c r="A8" s="2" t="str">
         <x:v>檢驗規範</x:v>
       </x:c>
-      <x:c r="P7" s="2" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="Q7" s="3" t="str">
-        <x:v>{{inspectSpec}}{{_str}}</x:v>
-      </x:c>
-      <x:c r="R7" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="S7" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="T7" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U7" s="3" t="str">
-        <x:v/>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="10" customHeight="1">
-      <x:c r="A8" s="3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="B8" s="3" t="str">
+      <x:c r="B8" s="2" t="str">
         <x:v/>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v/>
+        <x:v>{{inspectSpec}}</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
         <x:v/>
@@ -631,172 +642,230 @@
         <x:v/>
       </x:c>
     </x:row>
-    <x:row r="9" ht="20" customHeight="1">
-      <x:c r="A9" s="4" t="str">
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>子報表</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="L9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="M9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="N9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="O9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="P9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="Q9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="R9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="T9" s="6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U9" s="6" t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
+      <x:c r="A10" s="4" t="str">
         <x:v>項次</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="str">
+      <x:c r="B10" s="4" t="str">
         <x:v>檢驗項目</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="str">
+      <x:c r="C10" s="4" t="str">
         <x:v>點位</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="str">
+      <x:c r="D10" s="4" t="str">
         <x:v>標準值</x:v>
       </x:c>
-      <x:c r="E9" s="4" t="str">
+      <x:c r="E10" s="4" t="str">
         <x:v>下限</x:v>
       </x:c>
-      <x:c r="F9" s="4" t="str">
+      <x:c r="F10" s="4" t="str">
         <x:v>上限</x:v>
       </x:c>
-      <x:c r="G9" s="4" t="str">
+      <x:c r="G10" s="4" t="str">
         <x:v>量具</x:v>
       </x:c>
-      <x:c r="H9" s="4" t="str">
+      <x:c r="H10" s="4" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" s="4" t="str">
+      <x:c r="I10" s="4" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J9" s="4" t="str">
+      <x:c r="J10" s="4" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="str">
+      <x:c r="K10" s="4" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L9" s="4" t="str">
+      <x:c r="L10" s="4" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="M9" s="4" t="str">
+      <x:c r="M10" s="4" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N9" s="4" t="str">
+      <x:c r="N10" s="4" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="O9" s="4" t="str">
+      <x:c r="O10" s="4" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="str">
+      <x:c r="P10" s="4" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="Q9" s="4" t="str">
+      <x:c r="Q10" s="4" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="R9" s="4" t="str">
+      <x:c r="R10" s="4" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="S9" s="4" t="str">
+      <x:c r="S10" s="4" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="T9" s="4" t="str">
+      <x:c r="T10" s="4" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="U9" s="4" t="str">
+      <x:c r="U10" s="4" t="str">
         <x:v>檢驗結果</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="5" t="str">
-        <x:v>{{items.seq}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>{{items.itemName}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>{{items.point}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>{{items.std}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="str">
-        <x:v>{{items.lower}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="F10" s="5" t="str">
-        <x:v>{{items.upper}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="str">
-        <x:v>{{items.gauge}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>{{items.v1}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str">
-        <x:v>{{items.v2}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="J10" s="5" t="str">
-        <x:v>{{items.v3}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="K10" s="5" t="str">
-        <x:v>{{items.v4}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="L10" s="5" t="str">
-        <x:v>{{items.v5}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="M10" s="5" t="str">
-        <x:v>{{items.v6}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="N10" s="5" t="str">
-        <x:v>{{items.v7}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="O10" s="5" t="str">
-        <x:v>{{items.v8}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="str">
-        <x:v>{{items.v9}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="Q10" s="5" t="str">
-        <x:v>{{items.v10}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="R10" s="5" t="str">
-        <x:v>{{items.v11}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="S10" s="5" t="str">
-        <x:v>{{items.v12}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="T10" s="5" t="str">
-        <x:v>{{items.v13}}{{items._str}}</x:v>
-      </x:c>
-      <x:c r="U10" s="5" t="str">
-        <x:v>{{items.result}}{{items._str}}</x:v>
+    <x:row r="11" ht="18" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>{{items.seq}}</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>{{items.itemName}}</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>{{items.point}}</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>{{items.std}}</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="str">
+        <x:v>{{items.lower}}</x:v>
+      </x:c>
+      <x:c r="F11" s="5" t="str">
+        <x:v>{{items.upper}}</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="str">
+        <x:v>{{items.gauge}}</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
+        <x:v>{{items.v1}}</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="str">
+        <x:v>{{items.v2}}</x:v>
+      </x:c>
+      <x:c r="J11" s="5" t="str">
+        <x:v>{{items.v3}}</x:v>
+      </x:c>
+      <x:c r="K11" s="5" t="str">
+        <x:v>{{items.v4}}</x:v>
+      </x:c>
+      <x:c r="L11" s="5" t="str">
+        <x:v>{{items.v5}}</x:v>
+      </x:c>
+      <x:c r="M11" s="5" t="str">
+        <x:v>{{items.v6}}</x:v>
+      </x:c>
+      <x:c r="N11" s="5" t="str">
+        <x:v>{{items.v7}}</x:v>
+      </x:c>
+      <x:c r="O11" s="5" t="str">
+        <x:v>{{items.v8}}</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="str">
+        <x:v>{{items.v9}}</x:v>
+      </x:c>
+      <x:c r="Q11" s="5" t="str">
+        <x:v>{{items.v10}}</x:v>
+      </x:c>
+      <x:c r="R11" s="5" t="str">
+        <x:v>{{items.v11}}</x:v>
+      </x:c>
+      <x:c r="S11" s="5" t="str">
+        <x:v>{{items.v12}}</x:v>
+      </x:c>
+      <x:c r="T11" s="5" t="str">
+        <x:v>{{items.v13}}</x:v>
+      </x:c>
+      <x:c r="U11" s="5" t="str">
+        <x:v>{{items.result}}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:U1"/>
+    <x:mergeCell ref="A1:Q1"/>
+    <x:mergeCell ref="R1:U1"/>
     <x:mergeCell ref="A2:B2"/>
     <x:mergeCell ref="C2:G2"/>
     <x:mergeCell ref="H2:I2"/>
     <x:mergeCell ref="J2:N2"/>
     <x:mergeCell ref="O2:P2"/>
     <x:mergeCell ref="Q2:U2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:G3"/>
-    <x:mergeCell ref="H3:I3"/>
-    <x:mergeCell ref="J3:N3"/>
-    <x:mergeCell ref="O3:P3"/>
+    <x:mergeCell ref="B3:E3"/>
+    <x:mergeCell ref="G3:J3"/>
+    <x:mergeCell ref="L3:O3"/>
     <x:mergeCell ref="Q3:U3"/>
     <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:G4"/>
-    <x:mergeCell ref="H4:I4"/>
-    <x:mergeCell ref="J4:N4"/>
-    <x:mergeCell ref="O4:P4"/>
-    <x:mergeCell ref="Q4:U4"/>
+    <x:mergeCell ref="C4:J4"/>
+    <x:mergeCell ref="K4:L4"/>
+    <x:mergeCell ref="M4:U4"/>
     <x:mergeCell ref="A5:B5"/>
     <x:mergeCell ref="C5:U5"/>
-    <x:mergeCell ref="A6:B6"/>
-    <x:mergeCell ref="C6:G6"/>
-    <x:mergeCell ref="H6:I6"/>
-    <x:mergeCell ref="J6:N6"/>
-    <x:mergeCell ref="O6:P6"/>
+    <x:mergeCell ref="B6:E6"/>
+    <x:mergeCell ref="G6:J6"/>
+    <x:mergeCell ref="L6:O6"/>
     <x:mergeCell ref="Q6:U6"/>
     <x:mergeCell ref="A7:B7"/>
-    <x:mergeCell ref="C7:G7"/>
-    <x:mergeCell ref="H7:I7"/>
-    <x:mergeCell ref="J7:N7"/>
-    <x:mergeCell ref="O7:P7"/>
-    <x:mergeCell ref="Q7:U7"/>
-    <x:mergeCell ref="A8:U8"/>
+    <x:mergeCell ref="C7:U7"/>
+    <x:mergeCell ref="A8:B8"/>
+    <x:mergeCell ref="C8:U8"/>
+    <x:mergeCell ref="A9:U9"/>
   </x:mergeCells>
   <x:pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
